--- a/docs/client/ホテル個別設定ヒアリングシート_配布用.xlsx
+++ b/docs/client/ホテル個別設定ヒアリングシート_配布用.xlsx
@@ -13,7 +13,7 @@
     <sheet name="ご意見・ご要望" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ヒアリング項目'!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ヒアリング項目'!$A$1:$I$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C32"/>
+  <dimension ref="B2:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>v1.0（2026年9月）｜ 全94問（うち「必須」45問）</t>
+          <t>v1.1（2026年9月）｜ 全110問（うち「必須」51問）</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>初期設定に不可欠な項目です（45問）。お時間が取れない場合は「必須」のみでも結構です。E列の絞り込みでご確認いただけます。</t>
+          <t>初期設定に不可欠な項目です（51問）。お時間が取れない場合は「必須」のみでも結構です。I列の絞り込みでご確認いただけます。</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>全94問で40〜60分、「必須」のみですと20〜30分ほどです。</t>
+          <t>全110問で45〜70分、「必須」のみですと25〜35分ほどです。</t>
         </is>
       </c>
     </row>
@@ -722,86 +722,86 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>12 問（うち「必須」4 問）</t>
+          <t>13 問（うち「必須」5 問）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>5 問（うち「必須」3 問）</t>
+          <t>5 問（うち「必須」2 問）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>8 問（うち「必須」4 問）</t>
+          <t>7 問（うち「必須」4 問）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>14 問（うち「必須」6 問）</t>
+          <t>9 問（うち「必須」5 問）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>10 問（うち「必須」2 問）</t>
+          <t>16 問（うち「必須」6 問）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>15 問（うち「必須」11 問）</t>
+          <t>10 問（うち「必須」2 問）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>8 問（うち「必須」3 問）</t>
+          <t>15 問（うち「必須」11 問）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -813,12 +813,24 @@
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>9 問（うち「必須」4 問）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
           <t>運用体制</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>6 問（うち「必須」2 問）</t>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>10 問（うち「必須」2 問）</t>
         </is>
       </c>
     </row>
@@ -833,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1680,74 +1692,74 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>■ カレンダー</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>K-01</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>カレンダー</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>現在「週末」として扱っている曜日</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>金土,土日,金土日,その他</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>金土</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="12" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>M-13</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>指標定義</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>宿泊税・入湯税等はどのようにお取り扱いですか</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>料金に含む,別建て,課税なし</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>別建て</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>■ 予算・目標</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>K-02</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>「週末（曜日固定）」ではなく「休前日（翌日が休み）」で管理されたいですか</t>
+          <t>月次予算（売上・販売室数・ADR・稼働率・宿泊人数）をご提供いただけますか</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1757,12 +1769,12 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>休前日で管理したい,曜日固定でよい</t>
+          <t>提供できる,一部のみ,提供できない</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>休前日で管理したい</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="6" t="n"/>
@@ -1776,25 +1788,29 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>K-03</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>貴館固有の繁忙要因（近隣イベント・学会・受験期など）</t>
+          <t>前年実績を月次でご提供いただけますか</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>提供できる,一部のみ,提供できない</t>
+        </is>
+      </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1811,32 +1827,32 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>K-04</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>需要に効く季節要因（該当するものすべて）</t>
+          <t>予算の管理単位</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
+          <t>選択</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>春節 / 桜 / GW / 夏休み / 紅葉 / 年末年始 / 台風 / その他</t>
+          <t>施設全体のみ,客室タイプ別,セグメント別,併用</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>施設全体のみ</t>
         </is>
       </c>
       <c r="G28" s="6" t="n"/>
@@ -1850,102 +1866,110 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>K-05</t>
+          <t>B-04</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>カレンダー</t>
+          <t>予算・目標</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>天候が需要に影響する日数（何日前から効くか）</t>
+          <t>日別の予算（日割り）をお持ちですか</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>持っている,持っていない</t>
+        </is>
+      </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>7日</t>
+          <t>持っていない</t>
         </is>
       </c>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>任意</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>■ 料金ランク</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-      <c r="I30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>料金ランク</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>現在運用されている料金ランクの段階数</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>B-05</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>予算・目標</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>予算に対して最も重視される指標</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>売上,稼働率,ADR,RevPAR</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>売上</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>■ カレンダー</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>K-01</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>ランクの刻み幅</t>
+          <t>現在「週末」として扱っている曜日</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -1955,12 +1979,12 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>等比（%）,実額（円）,不定</t>
+          <t>金土,土日,金土日,その他</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>等比3〜5%/段</t>
+          <t>金土</t>
         </is>
       </c>
       <c r="G32" s="6" t="n"/>
@@ -1974,28 +1998,32 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>K-02</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>（等比の場合）1段あたりの%／（実額の場合）1段あたりの円</t>
+          <t>「週末（曜日固定）」ではなく「休前日（翌日が休み）」で管理されたいですか</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E33" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>休前日で管理したい,曜日固定でよい</t>
+        </is>
+      </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>休前日で管理したい</t>
         </is>
       </c>
       <c r="G33" s="6" t="n"/>
@@ -2009,71 +2037,67 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>K-03</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>中央ランク（標準価格）の考え方</t>
+          <t>貴館固有の繁忙要因（近隣イベント・学会・受験期など）</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>固定,月別に変える,設定なし</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr"/>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>固定</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>K-04</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>ランク表示の基準人数</t>
+          <t>需要に効く季節要因（該当するものすべて）</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
+          <t>自由記述</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>1名基準,2名基準</t>
+          <t>春節 / 桜 / GW / 夏休み / 紅葉 / 年末年始 / 台風 / その他</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>2名基準</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="6" t="n"/>
@@ -2087,67 +2111,63 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>K-05</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>人数別価格の倍率（1名を1.0とした2名/3名/4名）</t>
+          <t>天候が需要に影響する日数（何日前から効くか）</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
+          <t>数値</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr"/>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>1.7 / 1.35 / 1.2</t>
+          <t>7日</t>
         </is>
       </c>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>できれば</t>
+          <t>任意</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>K-06</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>部屋タイプ間の価格の持ち方</t>
+          <t>繁忙期・閑散期にあたる月をお聞かせください</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>標準タイプからの差額,タイプ別に独立したランク</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr"/>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>差額方式</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="6" t="n"/>
@@ -2161,17 +2181,17 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>K-07</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>料金ランク</t>
+          <t>カレンダー</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>実務上の上限ランク・下限ランク</t>
+          <t>休館日・大規模メンテナンスのご予定</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -2182,7 +2202,7 @@
       <c r="E38" s="11" t="inlineStr"/>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>下限R05 / 上限R38</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="6" t="n"/>
@@ -2196,7 +2216,7 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>■ 価格運用</t>
+          <t>■ 料金ランク</t>
         </is>
       </c>
       <c r="B39" s="9" t="n"/>
@@ -2211,32 +2231,28 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>価格決定の基本方針をお聞かせください　※最優先のご確認事項です</t>
+          <t>現在運用されている料金ランクの段階数</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>売上最大化,単価優先（稼働を落としても高単価）,前日より値下げしない,その他</t>
-        </is>
-      </c>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>売上最大化</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G40" s="6" t="n"/>
@@ -2250,28 +2266,32 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>V-02</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>上記の方針について、補足がございましたらお聞かせください</t>
+          <t>ランクの刻み幅</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>等比（%）,実額（円）,不定</t>
+        </is>
+      </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>等比3〜5%/段</t>
         </is>
       </c>
       <c r="G41" s="6" t="n"/>
@@ -2285,28 +2305,28 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>戦略の重み 稼働率（%）</t>
+          <t>（等比の場合）1段あたりの%／（実額の場合）1段あたりの円</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>自由記述</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr"/>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="6" t="n"/>
@@ -2320,98 +2340,106 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>V-04</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>戦略の重み ADR（%）</t>
+          <t>中央ランク（標準価格）の考え方</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>固定,月別に変える,設定なし</t>
+        </is>
+      </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>固定</t>
         </is>
       </c>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="6" t="n"/>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>V-05</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>戦略の重み 競合追従（%）※合計100</t>
+          <t>ランク表示の基準人数</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>1名基準,2名基準</t>
+        </is>
+      </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2名基準</t>
         </is>
       </c>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="6" t="n"/>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>V-06</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>1日あたりの価格変更幅の上限（ランク数）</t>
+          <t>人数別価格の倍率（1名を1.0とした2名/3名/4名）</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>数値</t>
+          <t>自由記述</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr"/>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.7 / 1.35 / 1.2</t>
         </is>
       </c>
       <c r="G45" s="6" t="n"/>
@@ -2425,17 +2453,17 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>V-07</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>値上げと値下げで変更幅を変えるか</t>
+          <t>部屋タイプ間の価格の持ち方</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -2445,51 +2473,47 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>変える,同じ</t>
+          <t>標準タイプからの差額,タイプ別に独立したランク</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>変える（上げ+2 / 下げ−1）</t>
+          <t>差額方式</t>
         </is>
       </c>
       <c r="G46" s="6" t="n"/>
       <c r="H46" s="6" t="n"/>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>V-08</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>最小の変更単位</t>
+          <t>実務上の上限ランク・下限ランク</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>1ランク,2ランク以上</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr"/>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>1ランク</t>
+          <t>下限R05 / 上限R38</t>
         </is>
       </c>
       <c r="G47" s="6" t="n"/>
@@ -2503,17 +2527,17 @@
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>V-09</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>価格運用</t>
+          <t>料金ランク</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>価格変更の頻度上限</t>
+          <t>現行の料金ランク表（各ランクの実額）をご提供いただけますか</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -2523,61 +2547,41 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>1日1回,1日2回,制限なし</t>
+          <t>提供できる,提供できない,作成中</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>1日1回（直前7日は2回）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="6" t="n"/>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>V-10</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>価格運用</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>繁忙日に段階的値上げを始める稼働率の節目</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>50 / 70 / 85%</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
-        </is>
-      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>■ 価格運用</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+      <c r="I49" s="9" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>V-11</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>残室が僅少（5%以下）のとき価格を上限で維持するか</t>
+          <t>価格決定の基本方針をお聞かせください　※最優先のご確認事項です</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -2597,26 +2601,26 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>維持する,通常どおり</t>
+          <t>売上最大化,単価優先（稼働を落としても高単価）,前日より値下げしない,その他</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>維持する</t>
+          <t>売上最大化</t>
         </is>
       </c>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="6" t="n"/>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>V-12</t>
+          <t>V-02</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -2626,22 +2630,18 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>直前（3日前以内）の値下げを認めるか</t>
+          <t>上記の方針について、補足がございましたらお聞かせください</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>条件付きで認める,認めない,制限なし</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr"/>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>条件付き</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="6" t="n"/>
@@ -2655,7 +2655,7 @@
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>V-13</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -2665,36 +2665,32 @@
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>価格の下限を原価から算出しているか</t>
+          <t>戦略の重み 稼働率（%）</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>算出している,していない</t>
-        </is>
-      </c>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr"/>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>していない</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="6" t="n"/>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>任意</t>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>V-14</t>
+          <t>V-04</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -2704,76 +2700,88 @@
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>返金不可プラン・早割プランの有無</t>
+          <t>戦略の重み ADR（%）</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>両方あり,早割のみ,返金不可のみ,なし</t>
-        </is>
-      </c>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr"/>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G53" s="6" t="n"/>
       <c r="H53" s="6" t="n"/>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>任意</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>■ 在庫・販売制限</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="n"/>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="9" t="n"/>
-      <c r="E54" s="9" t="n"/>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="9" t="n"/>
-      <c r="I54" s="9" t="n"/>
+      <c r="I53" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>V-05</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>価格運用</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>戦略の重み 競合追従（%）※合計100</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr"/>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="n"/>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>V-06</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>CTA（到着日クローズ）を使うか</t>
+          <t>1日あたりの価格変更幅の上限（ランク数）</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>使う,使わない</t>
-        </is>
-      </c>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr"/>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>使わない</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G55" s="6" t="n"/>
@@ -2787,17 +2795,17 @@
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>V-07</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>CTD（出発日クローズ）を使うか</t>
+          <t>値上げと値下げで変更幅を変えるか</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -2807,36 +2815,36 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>使う,使わない</t>
+          <t>変える,同じ</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>使わない</t>
+          <t>変える（上げ+2 / 下げ−1）</t>
         </is>
       </c>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="6" t="n"/>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>V-08</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>繁忙時に高手数料チャネルを売り止めるか</t>
+          <t>最小の変更単位</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -2846,12 +2854,12 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>売り止める,売り止めない</t>
+          <t>1ランク,2ランク以上</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>売り止める</t>
+          <t>1ランク</t>
         </is>
       </c>
       <c r="G57" s="6" t="n"/>
@@ -2865,102 +2873,106 @@
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>V-09</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>販売制限を解除する基準</t>
+          <t>価格変更の頻度上限</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>1日1回,1日2回,制限なし</t>
+        </is>
+      </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>7日前・残≥20%</t>
+          <t>1日1回（直前7日は2回）</t>
         </is>
       </c>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="6" t="n"/>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>V-10</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>オーバーブッキングを実施されていますか</t>
+          <t>繁忙日に段階的値上げを始める稼働率の節目</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>実施している,実施していない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr"/>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>実施していない</t>
+          <t>50 / 70 / 85%</t>
         </is>
       </c>
       <c r="G59" s="6" t="n"/>
       <c r="H59" s="6" t="n"/>
-      <c r="I59" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>S-06</t>
+          <t>V-11</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>実績のノーショー率（概算）</t>
+          <t>残室が僅少（5%以下）のとき価格を上限で維持するか</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>維持する,通常どおり</t>
+        </is>
+      </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>1%未満</t>
+          <t>維持する</t>
         </is>
       </c>
       <c r="G60" s="6" t="n"/>
@@ -2974,52 +2986,56 @@
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>S-07</t>
+          <t>V-12</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>団体ブロックの解放期限（団体種別ごとに）</t>
+          <t>直前（3日前以内）の値下げを認めるか</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>条件付きで認める,認めない,制限なし</t>
+        </is>
+      </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>繁忙60日前 / 閑散14日前</t>
+          <t>条件付き</t>
         </is>
       </c>
       <c r="G61" s="6" t="n"/>
       <c r="H61" s="6" t="n"/>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>S-08</t>
+          <t>V-13</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>直販用の在庫確保をしているか</t>
+          <t>価格の下限を原価から算出しているか</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
@@ -3029,7 +3045,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>サイトコントローラーで制御,していない,その他</t>
+          <t>算出している,していない</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -3041,59 +3057,63 @@
       <c r="H62" s="6" t="n"/>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>できれば</t>
+          <t>任意</t>
         </is>
       </c>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>S-09</t>
+          <t>V-14</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>キャンセルポリシー（無料期限・料率）</t>
+          <t>返金不可プラン・早割プランの有無</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>両方あり,早割のみ,返金不可のみ,なし</t>
+        </is>
+      </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="G63" s="6" t="n"/>
       <c r="H63" s="6" t="n"/>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>できれば</t>
+          <t>任意</t>
         </is>
       </c>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>V-15</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>在庫・販売制限</t>
+          <t>価格運用</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>利用中のサイトコントローラー名</t>
+          <t>需要レベル（A〜E）を判定する稼働率の目安</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -3104,120 +3124,120 @@
       <c r="E64" s="11" t="inlineStr"/>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A:85%以上 B:70% C:50% D:30% E:30%未満</t>
         </is>
       </c>
       <c r="G64" s="6" t="n"/>
       <c r="H64" s="6" t="n"/>
-      <c r="I64" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>■ データ連携</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="n"/>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="9" t="n"/>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="n"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>D-01</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="inlineStr">
-        <is>
-          <t>PMSから販売室数（部屋数）をご出力いただけますか　※最優先のご確認事項です</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>出せる,出せない,確認中</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>V-16</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>価格運用</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>リードタイムの区切り（何日前を境に運用を変えるか）</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr"/>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>60日 / 30日 / 14日 / 7日 / 3日</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>■ 在庫・販売制限</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
+      <c r="I66" s="9" t="n"/>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>PMSの製品名</t>
+          <t>CTA（到着日クローズ）を使うか</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>使う,使わない</t>
+        </is>
+      </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>使わない</t>
         </is>
       </c>
       <c r="G67" s="6" t="n"/>
       <c r="H67" s="6" t="n"/>
-      <c r="I67" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>予約データの出力形式</t>
+          <t>CTD（出発日クローズ）を使うか</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -3227,36 +3247,36 @@
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>xlsx,CSV,TSV,その他</t>
+          <t>使う,使わない</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>CSV</t>
+          <t>使わない</t>
         </is>
       </c>
       <c r="G68" s="6" t="n"/>
       <c r="H68" s="6" t="n"/>
-      <c r="I68" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>任意</t>
         </is>
       </c>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>出力の頻度</t>
+          <t>繁忙時に高手数料チャネルを売り止めるか</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -3266,36 +3286,36 @@
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>毎日,週次,都度手動</t>
+          <t>売り止める,売り止めない</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>毎日</t>
+          <t>売り止める</t>
         </is>
       </c>
       <c r="G69" s="6" t="n"/>
       <c r="H69" s="6" t="n"/>
-      <c r="I69" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>1日のうち何回・何時に出力できるか</t>
+          <t>販売制限を解除する基準</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -3306,31 +3326,31 @@
       <c r="E70" s="11" t="inlineStr"/>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>日次固定時刻（直前7日は朝夕2回）</t>
+          <t>7日前・残≥20%</t>
         </is>
       </c>
       <c r="G70" s="6" t="n"/>
       <c r="H70" s="6" t="n"/>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>できれば</t>
+          <t>任意</t>
         </is>
       </c>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>D-06</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>自動出力の可否</t>
+          <t>オーバーブッキングを実施されていますか</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -3340,12 +3360,12 @@
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>定時フォルダ配置,FTP,メール添付,手動のみ</t>
+          <t>実施している,実施していない</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>手動のみ</t>
+          <t>実施していない</t>
         </is>
       </c>
       <c r="G71" s="6" t="n"/>
@@ -3359,32 +3379,28 @@
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>D-07</t>
+          <t>S-06</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>差分抽出（予約変更日以降など）ができるか</t>
+          <t>実績のノーショー率（概算）</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>できる,できない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr"/>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>できない</t>
+          <t>1%未満</t>
         </is>
       </c>
       <c r="G72" s="6" t="n"/>
@@ -3398,17 +3414,17 @@
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>D-08</t>
+          <t>S-07</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>過去の実績データは何年分までさかのぼってご出力いただけますか</t>
+          <t>団体ブロックの解放期限（団体種別ごとに）</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -3419,31 +3435,31 @@
       <c r="E73" s="11" t="inlineStr"/>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>繁忙60日前 / 閑散14日前</t>
         </is>
       </c>
       <c r="G73" s="6" t="n"/>
       <c r="H73" s="6" t="n"/>
-      <c r="I73" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="74" ht="32" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>D-09</t>
+          <t>S-08</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>取消（CXL）レコードは出力に残り続けるか</t>
+          <t>直販用の在庫確保をしているか</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
@@ -3453,48 +3469,44 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>残る,消える,不明</t>
+          <t>サイトコントローラーで制御,していない,その他</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>残る</t>
+          <t>していない</t>
         </is>
       </c>
       <c r="G74" s="6" t="n"/>
       <c r="H74" s="6" t="n"/>
-      <c r="I74" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="75" ht="32" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>D-10</t>
+          <t>S-09</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>各明細行を一意に識別できる番号（明細番号など）をご出力いただけますか</t>
+          <t>キャンセルポリシー（無料期限・料率）</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>できる,できない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr"/>
       <c r="F75" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -3502,41 +3514,37 @@
       </c>
       <c r="G75" s="6" t="n"/>
       <c r="H75" s="6" t="n"/>
-      <c r="I75" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="76" ht="32" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>S-10</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>在庫・販売制限</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>泊ごとに人数が変わるご予約について、日別の人数データはございますか</t>
+          <t>利用中のサイトコントローラー名</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>取得できる,できない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr"/>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>できない</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G76" s="6" t="n"/>
@@ -3547,49 +3555,25 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>D-12</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>デイユース（泊数0）のレコードが存在するか</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>ある,ない</t>
-        </is>
-      </c>
-      <c r="F77" s="11" t="inlineStr">
-        <is>
-          <t>ない</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
-        </is>
-      </c>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>■ データ連携</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="9" t="n"/>
+      <c r="I77" s="9" t="n"/>
     </row>
     <row r="78" ht="32" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>D-13</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -3599,7 +3583,7 @@
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>部屋タイプコードの対応表を提供できるか</t>
+          <t>PMSから販売室数（部屋数）をご出力いただけますか　※最優先のご確認事項です</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -3609,7 +3593,7 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>できる,できない</t>
+          <t>出せる,出せない,確認中</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -3628,7 +3612,7 @@
     <row r="79" ht="32" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -3638,19 +3622,15 @@
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Market / エージェント / 地域コードの対応表を提供できるか</t>
+          <t>PMSの製品名</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>できる,できない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr"/>
       <c r="F79" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -3658,16 +3638,16 @@
       </c>
       <c r="G79" s="6" t="n"/>
       <c r="H79" s="6" t="n"/>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="80" ht="32" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>D-15</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -3677,7 +3657,7 @@
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>お客さまの個人情報（氏名・連絡先等）を連携対象に含めますか　※除外を推奨しております</t>
+          <t>予約データの出力形式</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -3687,12 +3667,12 @@
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>含めない,含める</t>
+          <t>xlsx,CSV,TSV,その他</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>含めない</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="G80" s="6" t="n"/>
@@ -3703,35 +3683,59 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>■ セグメント・団体</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="n"/>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="9" t="n"/>
-      <c r="F81" s="9" t="n"/>
-      <c r="G81" s="9" t="n"/>
-      <c r="H81" s="9" t="n"/>
-      <c r="I81" s="9" t="n"/>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>出力の頻度</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>毎日,週次,都度手動</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>毎日</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="n"/>
+      <c r="H81" s="6" t="n"/>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>セグメント区分（PMSのマスタ）を列挙</t>
+          <t>1日のうち何回・何時に出力できるか</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -3742,31 +3746,31 @@
       <c r="E82" s="11" t="inlineStr"/>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>日次固定時刻（直前7日は朝夕2回）</t>
         </is>
       </c>
       <c r="G82" s="6" t="n"/>
       <c r="H82" s="6" t="n"/>
-      <c r="I82" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>D-06</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>団体に「確度」を設定されていますか</t>
+          <t>自動出力の可否</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -3776,12 +3780,12 @@
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>設定している,していない</t>
+          <t>定時フォルダ配置,FTP,メール添付,手動のみ</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>していない</t>
+          <t>手動のみ</t>
         </is>
       </c>
       <c r="G83" s="6" t="n"/>
@@ -3795,28 +3799,32 @@
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>D-07</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>（設定している場合）確度の区分</t>
+          <t>差分抽出（予約変更日以降など）ができるか</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>できる,できない</t>
+        </is>
+      </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>ブロック / A / B / C</t>
+          <t>できない</t>
         </is>
       </c>
       <c r="G84" s="6" t="n"/>
@@ -3830,29 +3838,25 @@
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>D-08</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>団体ブロックのPMS上の持ち方</t>
+          <t>過去の実績データは何年分までさかのぼってご出力いただけますか</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>ブロック枠,実予約,仮予約,混在</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr"/>
       <c r="F85" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -3869,52 +3873,56 @@
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>G-05</t>
+          <t>D-09</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>ウォッシュ率（団体の実際の戻り率）の実績値</t>
+          <t>取消（CXL）レコードは出力に残り続けるか</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>残る,消える,不明</t>
+        </is>
+      </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>残る</t>
         </is>
       </c>
       <c r="G86" s="6" t="n"/>
       <c r="H86" s="6" t="n"/>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="87" ht="32" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>G-06</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>インバウンドの早期販売を制限しているか</t>
+          <t>各明細行を一意に識別できる番号（明細番号など）をご出力いただけますか</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
@@ -3924,36 +3932,36 @@
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>制限している,していない</t>
+          <t>できる,できない</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>していない</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G87" s="6" t="n"/>
       <c r="H87" s="6" t="n"/>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I87" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>D-11</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>月別のセグメントミックス目標があるか</t>
+          <t>泊ごとに人数が変わるご予約について、日別の人数データはございますか</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
@@ -3963,36 +3971,36 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>ある,ない</t>
+          <t>取得できる,できない</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>ない</t>
+          <t>できない</t>
         </is>
       </c>
       <c r="G88" s="6" t="n"/>
       <c r="H88" s="6" t="n"/>
-      <c r="I88" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="89" ht="32" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>G-08</t>
+          <t>D-12</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>セグメント・団体</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>団体を画面上で区別して表示する必要があるか</t>
+          <t>デイユース（泊数0）のレコードが存在するか</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
@@ -4002,59 +4010,87 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>必要,不要</t>
+          <t>ある,ない</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>必要</t>
+          <t>ない</t>
         </is>
       </c>
       <c r="G89" s="6" t="n"/>
       <c r="H89" s="6" t="n"/>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>任意</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>■ 競合・チャネル</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="9" t="n"/>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="9" t="n"/>
-      <c r="I90" s="9" t="n"/>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>部屋タイプコードの対応表を提供できるか</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>できる,できない</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="n"/>
+      <c r="H90" s="6" t="n"/>
+      <c r="I90" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>C-01</t>
+          <t>D-14</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>競合ホテル（最大5社）</t>
+          <t>Market / エージェント / 地域コードの対応表を提供できるか</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>できる,できない</t>
+        </is>
+      </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -4062,26 +4098,26 @@
       </c>
       <c r="G91" s="6" t="n"/>
       <c r="H91" s="6" t="n"/>
-      <c r="I91" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="92" ht="32" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>C-02</t>
+          <t>D-15</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>競合のOTA別URL（提供可否）</t>
+          <t>お客さまの個人情報（氏名・連絡先等）を連携対象に含めますか　※除外を推奨しております</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
@@ -4091,12 +4127,12 @@
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>提供できる,提供できない</t>
+          <t>含めない,含める</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>含めない</t>
         </is>
       </c>
       <c r="G92" s="6" t="n"/>
@@ -4107,133 +4143,109 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="32" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="inlineStr">
-        <is>
-          <t>競合・チャネル</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="inlineStr">
-        <is>
-          <t>競合比較の基準人数</t>
-        </is>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>1名,2名</t>
-        </is>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>2名</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="n"/>
-      <c r="H93" s="6" t="n"/>
-      <c r="I93" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>■ セグメント・団体</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="9" t="n"/>
     </row>
     <row r="94" ht="32" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>C-04</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>競合比較で食事条件を揃えるか</t>
+          <t>セグメント区分（PMSのマスタ）を列挙</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>食事なしで揃える,朝食付で揃える</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr"/>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>食事なし</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="6" t="n"/>
       <c r="H94" s="6" t="n"/>
-      <c r="I94" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>C-05</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>レートパリティの許容幅</t>
+          <t>団体に「確度」を設定されていますか</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>設定している,していない</t>
+        </is>
+      </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
-          <t>±3%</t>
+          <t>していない</t>
         </is>
       </c>
       <c r="G95" s="6" t="n"/>
       <c r="H95" s="6" t="n"/>
-      <c r="I95" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="96" ht="32" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>C-06</t>
+          <t>G-03</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>直販比率の目標値</t>
+          <t>（設定している場合）確度の区分</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -4244,7 +4256,7 @@
       <c r="E96" s="11" t="inlineStr"/>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>ブロック / A / B / C</t>
         </is>
       </c>
       <c r="G96" s="6" t="n"/>
@@ -4258,141 +4270,169 @@
     <row r="97" ht="32" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>C-07</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>繁忙日に絞りたいチャネル</t>
+          <t>団体ブロックのPMS上の持ち方</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>ブロック枠,実予約,仮予約,混在</t>
+        </is>
+      </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>高手数料チャネル</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="6" t="n"/>
       <c r="H97" s="6" t="n"/>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="98" ht="32" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>C-08</t>
+          <t>G-05</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>競合・チャネル</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>OTAとの特約（販促サポート等）の有無</t>
+          <t>ウォッシュ率（団体の実際の戻り率）の実績値</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>ある,ない</t>
-        </is>
-      </c>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr"/>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G98" s="6" t="n"/>
       <c r="H98" s="6" t="n"/>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>任意</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>■ 運用体制</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="n"/>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="9" t="n"/>
-      <c r="F99" s="9" t="n"/>
-      <c r="G99" s="9" t="n"/>
-      <c r="H99" s="9" t="n"/>
-      <c r="I99" s="9" t="n"/>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>G-06</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>セグメント・団体</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>インバウンドの早期販売を制限しているか</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>制限している,していない</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>していない</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="n"/>
+      <c r="H99" s="6" t="n"/>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="32" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>O-01</t>
+          <t>G-07</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>価格変更をご判断される方（役職・人数）</t>
+          <t>月別のセグメントミックス目標があるか</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>ある,ない</t>
+        </is>
+      </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ない</t>
         </is>
       </c>
       <c r="G100" s="6" t="n"/>
       <c r="H100" s="6" t="n"/>
-      <c r="I100" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
         </is>
       </c>
     </row>
     <row r="101" ht="32" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>O-02</t>
+          <t>G-08</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>セグメント・団体</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>価格見直しの頻度</t>
+          <t>団体を画面上で区別して表示する必要があるか</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
@@ -4402,75 +4442,51 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>毎日,週次,月次,不定期</t>
+          <t>必要,不要</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
-          <t>毎日</t>
+          <t>必要</t>
         </is>
       </c>
       <c r="G101" s="6" t="n"/>
       <c r="H101" s="6" t="n"/>
-      <c r="I101" s="12" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>O-03</t>
-        </is>
-      </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t>運用体制</t>
-        </is>
-      </c>
-      <c r="C102" s="11" t="inlineStr">
-        <is>
-          <t>「週次でご担当者さまが確認 → オペレーターさまが操作」という運用でよろしいですか</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>選択</t>
-        </is>
-      </c>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>よい,別の体制がよい</t>
-        </is>
-      </c>
-      <c r="F102" s="11" t="inlineStr">
-        <is>
-          <t>よい</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="n"/>
-      <c r="H102" s="6" t="n"/>
-      <c r="I102" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
-        </is>
-      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>■ 競合・チャネル</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="9" t="n"/>
+      <c r="I102" s="9" t="n"/>
     </row>
     <row r="103" ht="32" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>O-04</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>競合・チャネル</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>着地が予算を超過しそうなときの打ち手</t>
+          <t>競合ホテル（最大5社）</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
@@ -4486,26 +4502,26 @@
       </c>
       <c r="G103" s="6" t="n"/>
       <c r="H103" s="6" t="n"/>
-      <c r="I103" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="104" ht="32" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>O-05</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>競合・チャネル</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>利用人数別分析の区分</t>
+          <t>競合のOTA別URL（提供可否）</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
@@ -4515,60 +4531,659 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>1名/2名/3名以上,1名/2名/3名/4名以上,その他</t>
+          <t>提供できる,提供できない</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>1名/2名/3名以上</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G104" s="6" t="n"/>
       <c r="H104" s="6" t="n"/>
-      <c r="I104" s="11" t="inlineStr">
-        <is>
-          <t>できれば</t>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="105" ht="32" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>O-06</t>
+          <t>C-03</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>運用体制</t>
+          <t>競合・チャネル</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>システム利用者のロールと人数（管理者/マネージャー/オペレーター）</t>
+          <t>競合比較の基準人数</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>自由記述</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr"/>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>1名,2名</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2名</t>
         </is>
       </c>
       <c r="G105" s="6" t="n"/>
       <c r="H105" s="6" t="n"/>
-      <c r="I105" s="11" t="inlineStr">
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>競合比較で食事条件を揃えるか</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>食事なしで揃える,朝食付で揃える</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>食事なし</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="n"/>
+      <c r="H106" s="6" t="n"/>
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>できれば</t>
         </is>
       </c>
     </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>レートパリティの許容幅</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr"/>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>±3%</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="n"/>
+      <c r="H107" s="6" t="n"/>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>C-06</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>直販比率の目標値</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr"/>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="n"/>
+      <c r="H108" s="6" t="n"/>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>C-07</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>繁忙日に絞りたいチャネル</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr"/>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>高手数料チャネル</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="n"/>
+      <c r="H109" s="6" t="n"/>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>C-08</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>OTAとの特約（販促サポート等）の有無</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>ある,ない</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="n"/>
+      <c r="H110" s="6" t="n"/>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>C-09</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>競合・チャネル</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>現在販売されているチャネルの一覧をお聞かせください</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr"/>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="n"/>
+      <c r="H111" s="6" t="n"/>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>■ 運用体制</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="9" t="n"/>
+      <c r="H112" s="9" t="n"/>
+      <c r="I112" s="9" t="n"/>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>O-01</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>価格変更をご判断される方（役職・人数）</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr"/>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="n"/>
+      <c r="H113" s="6" t="n"/>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>O-02</t>
+        </is>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>価格見直しの頻度</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>毎日,週次,月次,不定期</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>毎日</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="n"/>
+      <c r="H114" s="6" t="n"/>
+      <c r="I114" s="12" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="32" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>O-03</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>「週次でご担当者さまが確認 → オペレーターさまが操作」という運用でよろしいですか</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>よい,別の体制がよい</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>よい</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="n"/>
+      <c r="H115" s="6" t="n"/>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>O-04</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>着地が予算を超過しそうなときの打ち手</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr"/>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="n"/>
+      <c r="H116" s="6" t="n"/>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>O-05</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>利用人数別分析の区分</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>1名/2名/3名以上,1名/2名/3名/4名以上,その他</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>1名/2名/3名以上</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="n"/>
+      <c r="H117" s="6" t="n"/>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>O-06</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>システム利用者のロールと人数（管理者/マネージャー/オペレーター）</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr"/>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="n"/>
+      <c r="H118" s="6" t="n"/>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>O-07</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>データ取込の操作を担当される方</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr"/>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="n"/>
+      <c r="H119" s="6" t="n"/>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>O-08</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>データ取込が何日途絶えたら警告を出すか</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr"/>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>2日</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="n"/>
+      <c r="H120" s="6" t="n"/>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>O-09</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>アラートの通知先・通知方法のご希望</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr"/>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>画面表示のみ</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="n"/>
+      <c r="H121" s="6" t="n"/>
+      <c r="I121" s="11" t="inlineStr">
+        <is>
+          <t>できれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>O-10</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>運用体制</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>イベントの影響度（大・中・小）の判断基準</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>自由記述</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr"/>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="n"/>
+      <c r="H122" s="6" t="n"/>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I105"/>
-  <dataValidations count="48">
+  <autoFilter ref="A1:I122"/>
+  <dataValidations count="54">
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ビジネス,シティ,リゾート,旅館,その他"</formula1>
     </dataValidation>
@@ -4584,7 +5199,7 @@
     <dataValidation sqref="G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"長期のみ除外,すべて除外,除外しない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G14 G15 G80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G14 G15 G92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"含めない,含める"</formula1>
     </dataValidation>
     <dataValidation sqref="G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4593,7 +5208,7 @@
     <dataValidation sqref="G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ある,ない,別システム"</formula1>
     </dataValidation>
-    <dataValidation sqref="G18 G89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G18 G101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"必要,不要"</formula1>
     </dataValidation>
     <dataValidation sqref="G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4608,109 +5223,127 @@
     <dataValidation sqref="G23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"売れなかった日は0として分母に含む,手動で補完する,除外する"</formula1>
     </dataValidation>
-    <dataValidation sqref="G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"料金に含む,別建て,課税なし"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G26 G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"提供できる,一部のみ,提供できない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"施設全体のみ,客室タイプ別,セグメント別,併用"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"持っている,持っていない"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"売上,稼働率,ADR,RevPAR"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"金土,土日,金土日,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"休前日で管理したい,曜日固定でよい"</formula1>
     </dataValidation>
-    <dataValidation sqref="G32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"等比（%）,実額（円）,不定"</formula1>
     </dataValidation>
-    <dataValidation sqref="G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"固定,月別に変える,設定なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1名基準,2名基準"</formula1>
     </dataValidation>
-    <dataValidation sqref="G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"標準タイプからの差額,タイプ別に独立したランク"</formula1>
     </dataValidation>
-    <dataValidation sqref="G40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"提供できる,提供できない,作成中"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"売上最大化,単価優先（稼働を落としても高単価）,前日より値下げしない,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"変える,同じ"</formula1>
     </dataValidation>
-    <dataValidation sqref="G47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1ランク,2ランク以上"</formula1>
     </dataValidation>
-    <dataValidation sqref="G48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1日1回,1日2回,制限なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="G50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"維持する,通常どおり"</formula1>
     </dataValidation>
-    <dataValidation sqref="G51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"条件付きで認める,認めない,制限なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"算出している,していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"両方あり,早割のみ,返金不可のみ,なし"</formula1>
     </dataValidation>
-    <dataValidation sqref="G55 G56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G67 G68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"使う,使わない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"売り止める,売り止めない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"実施している,実施していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"サイトコントローラーで制御,していない,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"出せる,出せない,確認中"</formula1>
     </dataValidation>
-    <dataValidation sqref="G68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"xlsx,CSV,TSV,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="G69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"毎日,週次,都度手動"</formula1>
     </dataValidation>
-    <dataValidation sqref="G71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"定時フォルダ配置,FTP,メール添付,手動のみ"</formula1>
     </dataValidation>
-    <dataValidation sqref="G72 G75 G78 G79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G84 G87 G90 G91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"できる,できない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"残る,消える,不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="G76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"取得できる,できない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G77 G88 G98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G89 G100 G110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ある,ない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"設定している,していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ブロック枠,実予約,仮予約,混在"</formula1>
     </dataValidation>
-    <dataValidation sqref="G87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"制限している,していない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"提供できる,提供できない"</formula1>
     </dataValidation>
-    <dataValidation sqref="G93" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G105" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1名,2名"</formula1>
     </dataValidation>
-    <dataValidation sqref="G94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"食事なしで揃える,朝食付で揃える"</formula1>
     </dataValidation>
-    <dataValidation sqref="G101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"毎日,週次,月次,不定期"</formula1>
     </dataValidation>
-    <dataValidation sqref="G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"よい,別の体制がよい"</formula1>
     </dataValidation>
-    <dataValidation sqref="G104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1名/2名/3名以上,1名/2名/3名/4名以上,その他"</formula1>
     </dataValidation>
   </dataValidations>
